--- a/data/trans_dic/P16A11-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A11-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,75; 16,07</t>
+          <t>9,03; 16,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,38; 16,6</t>
+          <t>8,0; 16,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,88; 14,46</t>
+          <t>7,1; 14,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,26; 24,17</t>
+          <t>15,38; 24,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,69; 19,09</t>
+          <t>10,77; 19,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,6; 20,64</t>
+          <t>11,6; 20,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,07; 17,35</t>
+          <t>9,03; 16,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,33; 22,0</t>
+          <t>15,17; 22,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,88; 16,8</t>
+          <t>10,88; 16,4</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,85; 17,05</t>
+          <t>11,1; 17,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,79; 14,08</t>
+          <t>8,89; 14,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,34; 21,88</t>
+          <t>16,38; 21,72</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,37; 14,04</t>
+          <t>8,53; 14,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,45; 19,46</t>
+          <t>12,87; 19,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,75; 19,67</t>
+          <t>12,94; 19,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,01; 19,1</t>
+          <t>12,2; 18,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,6; 21,18</t>
+          <t>14,73; 21,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,02; 24,29</t>
+          <t>17,24; 24,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,86; 26,72</t>
+          <t>18,94; 26,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,65; 17,88</t>
+          <t>12,49; 17,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,34; 16,73</t>
+          <t>12,03; 16,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,84; 20,89</t>
+          <t>15,71; 20,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,84; 22,02</t>
+          <t>17,16; 22,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,1; 17,15</t>
+          <t>13,02; 17,2</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,36; 17,58</t>
+          <t>9,98; 17,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,15; 23,53</t>
+          <t>13,96; 22,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,15; 19,77</t>
+          <t>11,44; 19,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,95; 26,09</t>
+          <t>18,04; 25,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,61; 24,64</t>
+          <t>15,69; 24,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,38; 27,29</t>
+          <t>18,75; 27,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,11; 19,94</t>
+          <t>11,79; 19,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,53; 27,87</t>
+          <t>20,6; 27,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,98; 19,66</t>
+          <t>14,12; 19,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,65; 24,05</t>
+          <t>17,74; 24,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,87; 18,42</t>
+          <t>12,77; 18,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,51; 26,17</t>
+          <t>20,17; 25,69</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,0; 17,07</t>
+          <t>10,05; 16,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,57; 22,97</t>
+          <t>14,38; 22,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,32; 20,89</t>
+          <t>13,43; 21,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,46; 24,6</t>
+          <t>15,93; 25,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,38; 21,99</t>
+          <t>14,64; 22,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,47; 29,55</t>
+          <t>20,79; 29,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,92; 25,99</t>
+          <t>17,19; 26,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,35; 22,41</t>
+          <t>10,82; 22,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,24; 18,41</t>
+          <t>13,31; 18,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,73; 24,82</t>
+          <t>18,46; 24,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,38; 22,55</t>
+          <t>16,2; 22,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,56; 21,87</t>
+          <t>13,24; 21,86</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,64; 13,34</t>
+          <t>5,31; 13,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,86; 20,97</t>
+          <t>10,8; 21,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,11; 15,91</t>
+          <t>7,27; 16,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,16; 23,75</t>
+          <t>14,93; 24,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,89; 17,78</t>
+          <t>7,73; 17,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,31; 32,76</t>
+          <t>20,69; 32,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,58; 25,64</t>
+          <t>14,7; 25,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,09; 30,43</t>
+          <t>22,56; 30,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,85; 13,94</t>
+          <t>7,72; 13,77</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,15; 25,06</t>
+          <t>17,06; 25,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,8; 18,82</t>
+          <t>12,1; 18,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,33; 26,23</t>
+          <t>20,25; 26,11</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,48; 20,26</t>
+          <t>11,51; 19,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,31; 28,59</t>
+          <t>17,68; 28,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,68; 18,65</t>
+          <t>10,03; 18,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,19; 32,15</t>
+          <t>23,13; 32,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,88; 24,81</t>
+          <t>14,81; 23,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,24; 28,2</t>
+          <t>17,92; 27,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,67; 21,82</t>
+          <t>12,48; 21,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,08; 27,4</t>
+          <t>20,07; 27,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,62; 20,89</t>
+          <t>14,08; 20,75</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19,41; 26,5</t>
+          <t>19,54; 26,55</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12,27; 18,5</t>
+          <t>12,22; 18,26</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22,68; 28,41</t>
+          <t>22,6; 28,27</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,59; 17,54</t>
+          <t>11,97; 17,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,33; 21,2</t>
+          <t>15,59; 21,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,09; 17,68</t>
+          <t>12,04; 17,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,68; 20,74</t>
+          <t>14,68; 20,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,68; 21,45</t>
+          <t>15,42; 21,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,43; 26,22</t>
+          <t>19,99; 26,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,59; 16,89</t>
+          <t>11,62; 17,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,98; 65,7</t>
+          <t>18,56; 69,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,66; 18,82</t>
+          <t>14,38; 18,53</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,25; 22,61</t>
+          <t>18,6; 23,1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,62; 16,71</t>
+          <t>12,54; 16,63</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,11; 57,96</t>
+          <t>17,95; 54,42</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,54; 14,08</t>
+          <t>9,56; 14,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,71; 16,97</t>
+          <t>11,75; 17,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,72; 18,89</t>
+          <t>13,84; 18,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,97; 19,34</t>
+          <t>6,04; 19,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,77; 15,78</t>
+          <t>10,93; 16,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,71; 19,12</t>
+          <t>14,03; 19,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,8; 21,74</t>
+          <t>15,83; 21,68</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>19,83; 25,06</t>
+          <t>19,95; 25,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,81; 14,28</t>
+          <t>10,79; 14,32</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13,62; 17,26</t>
+          <t>13,62; 17,2</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15,49; 19,45</t>
+          <t>15,57; 19,58</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,62; 20,89</t>
+          <t>10,33; 20,92</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11,59; 13,9</t>
+          <t>11,58; 13,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15,25; 18,04</t>
+          <t>15,4; 18,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,68; 16,1</t>
+          <t>13,69; 16,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,67; 19,62</t>
+          <t>13,55; 19,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,41; 18,08</t>
+          <t>15,54; 18,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,62; 22,32</t>
+          <t>19,56; 22,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,43; 19,11</t>
+          <t>16,43; 19,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19,8; 39,36</t>
+          <t>19,73; 37,9</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13,84; 15,6</t>
+          <t>13,86; 15,63</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17,85; 19,77</t>
+          <t>17,93; 19,84</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15,46; 17,33</t>
+          <t>15,44; 17,24</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,5; 30,12</t>
+          <t>18,35; 30,39</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23892; 43863</t>
+          <t>24640; 45246</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24546; 48627</t>
+          <t>23434; 46934</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20196; 42466</t>
+          <t>20858; 42119</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47516; 75286</t>
+          <t>47911; 75835</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27893; 49802</t>
+          <t>28087; 50697</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32738; 58280</t>
+          <t>32743; 58104</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26179; 50092</t>
+          <t>26079; 48821</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44396; 63730</t>
+          <t>43938; 63929</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58062; 89675</t>
+          <t>58094; 87558</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62407; 98104</t>
+          <t>63835; 98250</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51194; 82013</t>
+          <t>51782; 84671</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>98207; 131493</t>
+          <t>98452; 130547</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41272; 69228</t>
+          <t>42044; 69349</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62914; 98400</t>
+          <t>65073; 99898</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64093; 98849</t>
+          <t>65035; 98901</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62046; 98634</t>
+          <t>63007; 96811</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>73558; 106749</t>
+          <t>74238; 108751</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>88994; 126953</t>
+          <t>90129; 128847</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>98657; 139749</t>
+          <t>99053; 138894</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>65002; 91863</t>
+          <t>64161; 90727</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>122994; 166783</t>
+          <t>119971; 167360</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>162829; 214775</t>
+          <t>161578; 209812</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>172683; 225841</t>
+          <t>176022; 227801</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>134970; 176725</t>
+          <t>134113; 177230</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33048; 56055</t>
+          <t>31820; 55918</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>45710; 76016</t>
+          <t>45091; 74277</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38721; 62988</t>
+          <t>36438; 61039</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56736; 82446</t>
+          <t>57025; 81463</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>52364; 82636</t>
+          <t>52631; 81118</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62695; 93060</t>
+          <t>63935; 94764</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37365; 67069</t>
+          <t>39659; 66864</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>71665; 97294</t>
+          <t>71935; 97417</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>91470; 128608</t>
+          <t>92364; 128796</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>117205; 159711</t>
+          <t>117805; 159745</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>84270; 120636</t>
+          <t>83655; 120645</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>136456; 174070</t>
+          <t>134185; 170901</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35880; 61208</t>
+          <t>36063; 60414</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>54475; 85896</t>
+          <t>53772; 84511</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49289; 77284</t>
+          <t>49685; 78029</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48329; 76892</t>
+          <t>49783; 78782</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>53398; 81676</t>
+          <t>54375; 83236</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79433; 114648</t>
+          <t>80677; 115099</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>65522; 100650</t>
+          <t>66591; 101983</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49216; 106630</t>
+          <t>51490; 108234</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>96639; 134437</t>
+          <t>97207; 133742</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>142678; 189114</t>
+          <t>140622; 187884</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>124018; 170750</t>
+          <t>122687; 169634</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>106867; 172408</t>
+          <t>104351; 172297</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11471; 27120</t>
+          <t>10786; 26771</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>23083; 44585</t>
+          <t>22956; 45566</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15010; 33597</t>
+          <t>15355; 34723</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27092; 42453</t>
+          <t>26688; 43513</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16384; 36921</t>
+          <t>16060; 35902</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44602; 71936</t>
+          <t>45442; 72038</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31862; 56053</t>
+          <t>32138; 55945</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>48179; 63502</t>
+          <t>47063; 64378</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>32262; 57274</t>
+          <t>31746; 56571</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>74108; 108315</t>
+          <t>73730; 110764</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50701; 80907</t>
+          <t>51997; 80490</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>78766; 101609</t>
+          <t>78454; 101160</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>31083; 54873</t>
+          <t>31177; 53687</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>50174; 78325</t>
+          <t>48450; 77659</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25467; 49083</t>
+          <t>26382; 47741</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>62523; 86698</t>
+          <t>62377; 86420</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>41393; 68999</t>
+          <t>41192; 65681</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>50914; 78713</t>
+          <t>50027; 77703</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34613; 59598</t>
+          <t>34079; 58599</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>51620; 70421</t>
+          <t>51598; 70633</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>80251; 114658</t>
+          <t>77277; 113899</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>107379; 146597</t>
+          <t>108072; 146865</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65820; 99212</t>
+          <t>65535; 97936</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>119460; 149624</t>
+          <t>119026; 148919</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>71297; 107892</t>
+          <t>73635; 108861</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>101609; 140512</t>
+          <t>103299; 143344</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>79371; 116065</t>
+          <t>79019; 116718</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>91645; 129491</t>
+          <t>91634; 129153</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>100080; 136919</t>
+          <t>98386; 139451</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>134823; 181951</t>
+          <t>138685; 181731</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>80121; 116778</t>
+          <t>80361; 120006</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>161194; 557995</t>
+          <t>157596; 587135</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>183703; 235919</t>
+          <t>180169; 232259</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>247534; 306763</t>
+          <t>252315; 313436</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>170076; 225255</t>
+          <t>169055; 224127</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>266907; 854083</t>
+          <t>264543; 801865</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>70891; 104585</t>
+          <t>70989; 105813</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>91012; 131814</t>
+          <t>91307; 132187</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>106790; 147097</t>
+          <t>107778; 147670</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>55473; 179654</t>
+          <t>56136; 177018</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>84387; 123653</t>
+          <t>85676; 127165</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>112445; 156892</t>
+          <t>115126; 158760</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>130564; 179597</t>
+          <t>130793; 179117</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>141768; 179168</t>
+          <t>142612; 179945</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>164976; 217924</t>
+          <t>164627; 218594</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>217498; 275684</t>
+          <t>217640; 274793</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>248593; 312185</t>
+          <t>249916; 314210</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>174550; 343384</t>
+          <t>169733; 343874</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>379776; 455223</t>
+          <t>379184; 449429</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>521960; 617425</t>
+          <t>527150; 617562</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>464438; 546579</t>
+          <t>464682; 550516</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>472651; 678362</t>
+          <t>468711; 672069</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>520780; 611006</t>
+          <t>525033; 608714</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>695928; 791566</t>
+          <t>693845; 796944</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>582339; 677238</t>
+          <t>582402; 675898</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>724417; 1439981</t>
+          <t>721775; 1386413</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>920899; 1037997</t>
+          <t>922669; 1040186</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1243721; 1377777</t>
+          <t>1249357; 1382581</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1072519; 1202296</t>
+          <t>1071688; 1196193</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1316310; 2143246</t>
+          <t>1305539; 2162816</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A11-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A11-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,03; 16,57</t>
+          <t>8,72; 16,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,0; 16,02</t>
+          <t>8,29; 16,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,1; 14,34</t>
+          <t>7,02; 14,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,38; 24,35</t>
+          <t>16,38; 25,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,77; 19,44</t>
+          <t>10,81; 19,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,6; 20,58</t>
+          <t>11,95; 20,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,03; 16,91</t>
+          <t>8,86; 17,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,17; 22,07</t>
+          <t>14,36; 20,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,88; 16,4</t>
+          <t>10,67; 16,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,1; 17,08</t>
+          <t>10,96; 17,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,89; 14,54</t>
+          <t>8,81; 14,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,38; 21,72</t>
+          <t>16,54; 22,06</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,53; 14,06</t>
+          <t>8,17; 14,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,87; 19,76</t>
+          <t>12,65; 19,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,94; 19,68</t>
+          <t>12,75; 19,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,2; 18,74</t>
+          <t>11,87; 18,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,73; 21,58</t>
+          <t>14,8; 21,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,24; 24,65</t>
+          <t>17,02; 24,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,94; 26,55</t>
+          <t>19,12; 26,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,49; 17,66</t>
+          <t>12,68; 17,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,03; 16,79</t>
+          <t>12,28; 16,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,71; 20,4</t>
+          <t>15,95; 20,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,16; 22,21</t>
+          <t>17,06; 21,97</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,02; 17,2</t>
+          <t>12,96; 16,95</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,98; 17,54</t>
+          <t>10,18; 17,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,96; 22,99</t>
+          <t>14,17; 23,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,44; 19,16</t>
+          <t>11,73; 19,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,04; 25,78</t>
+          <t>18,01; 25,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,69; 24,18</t>
+          <t>15,0; 23,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,75; 27,79</t>
+          <t>18,51; 27,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,79; 19,88</t>
+          <t>11,96; 20,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,6; 27,9</t>
+          <t>20,38; 27,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,12; 19,69</t>
+          <t>14,01; 19,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,74; 24,05</t>
+          <t>17,74; 24,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,77; 18,42</t>
+          <t>12,9; 18,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,17; 25,69</t>
+          <t>20,22; 25,4</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,05; 16,84</t>
+          <t>10,03; 16,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,38; 22,6</t>
+          <t>14,2; 22,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,43; 21,09</t>
+          <t>13,22; 20,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,93; 25,21</t>
+          <t>14,65; 23,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,64; 22,41</t>
+          <t>14,52; 22,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,79; 29,67</t>
+          <t>20,82; 29,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,19; 26,33</t>
+          <t>17,07; 26,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,82; 22,75</t>
+          <t>18,25; 24,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,31; 18,32</t>
+          <t>13,27; 18,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,46; 24,66</t>
+          <t>18,57; 24,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,2; 22,4</t>
+          <t>16,51; 22,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,24; 21,86</t>
+          <t>17,55; 22,68</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,31; 13,17</t>
+          <t>5,46; 13,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,8; 21,43</t>
+          <t>10,91; 21,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,27; 16,44</t>
+          <t>7,09; 16,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,93; 24,34</t>
+          <t>13,77; 21,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,73; 17,29</t>
+          <t>7,91; 17,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,69; 32,81</t>
+          <t>21,08; 32,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,7; 25,59</t>
+          <t>14,37; 25,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,56; 30,85</t>
+          <t>21,78; 28,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,72; 13,77</t>
+          <t>7,49; 13,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,06; 25,63</t>
+          <t>16,98; 24,97</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,1; 18,73</t>
+          <t>12,0; 18,72</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,25; 26,11</t>
+          <t>18,87; 24,53</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,3%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,51; 19,82</t>
+          <t>11,58; 20,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,68; 28,34</t>
+          <t>17,93; 28,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,03; 18,14</t>
+          <t>10,23; 18,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,13; 32,05</t>
+          <t>22,87; 31,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,81; 23,61</t>
+          <t>14,63; 24,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,92; 27,84</t>
+          <t>18,36; 28,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,48; 21,46</t>
+          <t>12,36; 22,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,07; 27,48</t>
+          <t>20,05; 27,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,08; 20,75</t>
+          <t>14,04; 20,74</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19,54; 26,55</t>
+          <t>19,42; 26,55</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12,22; 18,26</t>
+          <t>12,22; 18,45</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22,6; 28,27</t>
+          <t>22,61; 28,34</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,97; 17,7</t>
+          <t>11,98; 17,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,59; 21,63</t>
+          <t>15,11; 21,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,04; 17,78</t>
+          <t>12,17; 17,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,68; 20,69</t>
+          <t>15,45; 21,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,42; 21,85</t>
+          <t>15,54; 21,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,99; 26,19</t>
+          <t>19,48; 26,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,62; 17,36</t>
+          <t>11,67; 17,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,56; 69,13</t>
+          <t>18,07; 22,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,38; 18,53</t>
+          <t>14,61; 18,77</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,6; 23,1</t>
+          <t>18,33; 22,86</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,54; 16,63</t>
+          <t>12,67; 16,53</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,95; 54,42</t>
+          <t>17,46; 21,24</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,56; 14,25</t>
+          <t>9,55; 14,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,75; 17,01</t>
+          <t>11,65; 16,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,84; 18,97</t>
+          <t>13,62; 19,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,04; 19,06</t>
+          <t>15,17; 20,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,93; 16,23</t>
+          <t>10,87; 15,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,03; 19,35</t>
+          <t>14,08; 19,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,83; 21,68</t>
+          <t>15,63; 21,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>19,95; 25,17</t>
+          <t>18,95; 23,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,79; 14,32</t>
+          <t>11,01; 14,32</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13,62; 17,2</t>
+          <t>13,56; 17,29</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15,57; 19,58</t>
+          <t>15,36; 19,48</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,33; 20,92</t>
+          <t>17,86; 21,24</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11,58; 13,72</t>
+          <t>11,61; 13,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15,4; 18,05</t>
+          <t>15,38; 18,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,69; 16,22</t>
+          <t>13,57; 15,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,55; 19,44</t>
+          <t>17,52; 19,97</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,54; 18,01</t>
+          <t>15,53; 18,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,56; 22,47</t>
+          <t>19,46; 22,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,43; 19,07</t>
+          <t>16,42; 19,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19,73; 37,9</t>
+          <t>19,48; 21,53</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13,86; 15,63</t>
+          <t>13,76; 15,46</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17,93; 19,84</t>
+          <t>17,93; 19,82</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15,44; 17,24</t>
+          <t>15,46; 17,32</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,35; 30,39</t>
+          <t>18,86; 20,43</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60448</t>
+          <t>66625</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>53598</t>
+          <t>55202</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>114046</t>
+          <t>121827</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24640; 45246</t>
+          <t>23793; 44841</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23434; 46934</t>
+          <t>24287; 47246</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20858; 42119</t>
+          <t>20634; 41887</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47911; 75835</t>
+          <t>52234; 80557</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28087; 50697</t>
+          <t>28188; 50424</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32743; 58104</t>
+          <t>33729; 58814</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26079; 48821</t>
+          <t>25572; 49170</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>43938; 63929</t>
+          <t>45397; 64493</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58094; 87558</t>
+          <t>56962; 86657</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>63835; 98250</t>
+          <t>63064; 98050</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51782; 84671</t>
+          <t>51343; 83450</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>98452; 130547</t>
+          <t>104993; 140091</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78392</t>
+          <t>79850</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>77097</t>
+          <t>82827</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>155489</t>
+          <t>162677</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42044; 69349</t>
+          <t>40294; 69178</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65073; 99898</t>
+          <t>63953; 100069</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65035; 98901</t>
+          <t>64092; 98235</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>63007; 96811</t>
+          <t>62786; 99234</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>74238; 108751</t>
+          <t>74575; 107577</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>90129; 128847</t>
+          <t>88964; 126393</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>99053; 138894</t>
+          <t>99997; 139673</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64161; 90727</t>
+          <t>69148; 96639</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>119971; 167360</t>
+          <t>122465; 167710</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>161578; 209812</t>
+          <t>164038; 214843</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>176022; 227801</t>
+          <t>174968; 225326</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>134113; 177230</t>
+          <t>139197; 182001</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68711</t>
+          <t>67838</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83770</t>
+          <t>84918</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>152481</t>
+          <t>152756</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31820; 55918</t>
+          <t>32460; 57244</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>45091; 74277</t>
+          <t>45786; 75096</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36438; 61039</t>
+          <t>37371; 62183</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57025; 81463</t>
+          <t>56914; 81497</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>52631; 81118</t>
+          <t>50304; 80002</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63935; 94764</t>
+          <t>63132; 95308</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39659; 66864</t>
+          <t>40239; 67411</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>71935; 97417</t>
+          <t>72637; 97682</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>92364; 128796</t>
+          <t>91642; 128819</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>117805; 159745</t>
+          <t>117839; 159992</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>83655; 120645</t>
+          <t>84463; 119698</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>134185; 170901</t>
+          <t>135922; 170776</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62210</t>
+          <t>69025</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>82961</t>
+          <t>89778</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>145171</t>
+          <t>158803</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36063; 60414</t>
+          <t>35992; 59831</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53772; 84511</t>
+          <t>53087; 84723</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49685; 78029</t>
+          <t>48920; 77672</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49783; 78782</t>
+          <t>54648; 86817</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54375; 83236</t>
+          <t>53936; 83178</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>80677; 115099</t>
+          <t>80762; 114009</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66591; 101983</t>
+          <t>66107; 102846</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51490; 108234</t>
+          <t>77013; 103921</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>97207; 133742</t>
+          <t>96872; 133736</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>140622; 187884</t>
+          <t>141494; 187998</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>122687; 169634</t>
+          <t>125037; 169229</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>104351; 172297</t>
+          <t>139543; 180346</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34166</t>
+          <t>36407</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>55302</t>
+          <t>57351</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89468</t>
+          <t>93757</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10786; 26771</t>
+          <t>11100; 26922</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22956; 45566</t>
+          <t>23194; 44772</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15355; 34723</t>
+          <t>14975; 34068</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26688; 43513</t>
+          <t>28323; 45209</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16060; 35902</t>
+          <t>16418; 35452</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>45442; 72038</t>
+          <t>46290; 70917</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32138; 55945</t>
+          <t>31420; 54880</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>47063; 64378</t>
+          <t>49476; 65697</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>31746; 56571</t>
+          <t>30801; 56004</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>73730; 110764</t>
+          <t>73390; 107935</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51997; 80490</t>
+          <t>51558; 80478</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>78454; 101160</t>
+          <t>81666; 106182</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>73811</t>
+          <t>72786</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>60405</t>
+          <t>62430</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>134216</t>
+          <t>135217</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>31177; 53687</t>
+          <t>31352; 55616</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>48450; 77659</t>
+          <t>49120; 78354</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26382; 47741</t>
+          <t>26924; 47639</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>62377; 86420</t>
+          <t>61899; 85713</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>41192; 65681</t>
+          <t>40696; 67435</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>50027; 77703</t>
+          <t>51255; 79439</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34079; 58599</t>
+          <t>33768; 60185</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>51598; 70633</t>
+          <t>52878; 72490</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>77277; 113899</t>
+          <t>77082; 113827</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>108072; 146865</t>
+          <t>107432; 146829</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65535; 97936</t>
+          <t>65546; 98945</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>119026; 148919</t>
+          <t>120843; 151483</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>110350</t>
+          <t>130503</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>330471</t>
+          <t>157926</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>440820</t>
+          <t>288429</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>73635; 108861</t>
+          <t>73672; 107545</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>103299; 143344</t>
+          <t>100173; 145171</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>79019; 116718</t>
+          <t>79892; 116081</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>91634; 129153</t>
+          <t>111194; 155126</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>98386; 139451</t>
+          <t>99175; 139191</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>138685; 181731</t>
+          <t>135130; 182545</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>80361; 120006</t>
+          <t>80701; 118318</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>157596; 587135</t>
+          <t>139496; 177059</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>180169; 232259</t>
+          <t>183125; 235190</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>252315; 313436</t>
+          <t>248664; 310174</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>169055; 224127</t>
+          <t>170718; 222790</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>264543; 801865</t>
+          <t>260481; 316812</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>125251</t>
+          <t>140046</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>159037</t>
+          <t>175791</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>284288</t>
+          <t>315837</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>70989; 105813</t>
+          <t>70940; 104692</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>91307; 132187</t>
+          <t>90549; 131059</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>107778; 147670</t>
+          <t>106067; 148760</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>56136; 177018</t>
+          <t>121074; 160436</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>85676; 127165</t>
+          <t>85170; 124549</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>115126; 158760</t>
+          <t>115472; 160768</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>130793; 179117</t>
+          <t>129152; 178191</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>142612; 179945</t>
+          <t>157287; 196858</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>164627; 218594</t>
+          <t>168036; 218589</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>217640; 274793</t>
+          <t>216681; 276184</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>249916; 314210</t>
+          <t>246503; 312594</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>169733; 343874</t>
+          <t>290804; 345789</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>613339</t>
+          <t>663080</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>902641</t>
+          <t>766222</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1515979</t>
+          <t>1429302</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>379184; 449429</t>
+          <t>380247; 452546</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>527150; 617562</t>
+          <t>526209; 616452</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>464682; 550516</t>
+          <t>460657; 542765</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>468711; 672069</t>
+          <t>618741; 705213</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>525033; 608714</t>
+          <t>524789; 611644</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>693845; 796944</t>
+          <t>690133; 794399</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>582402; 675898</t>
+          <t>581873; 681888</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>721775; 1386413</t>
+          <t>726964; 803573</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>922669; 1040186</t>
+          <t>915783; 1028937</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1249357; 1382581</t>
+          <t>1249622; 1381315</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1071688; 1196193</t>
+          <t>1072991; 1201570</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1305539; 2162816</t>
+          <t>1369921; 1483872</t>
         </is>
       </c>
     </row>
